--- a/ricette.xlsx
+++ b/ricette.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ricette!$A$1:$G$3</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -174,16 +174,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -269,6 +269,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -461,93 +465,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>20</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>60</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
